--- a/ig/test-tabs-svs/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/test-tabs-svs/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260601120000</t>
+    <t>20260629120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:00:00+01:00</t>
+    <t>2026-06-29T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>1630</t>
+    <t>1687</t>
   </si>
   <si>
     <t>Code</t>
